--- a/output/pdf_financials_xlsx/CEU.xlsx
+++ b/output/pdf_financials_xlsx/CEU.xlsx
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>33.357</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>25.761</v>
+        <v>12.371</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>14.275</v>
@@ -16872,7 +16872,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">

--- a/output/pdf_financials_xlsx/CEU.xlsx
+++ b/output/pdf_financials_xlsx/CEU.xlsx
@@ -5819,22 +5819,22 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>2.534</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>5.244</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>6.374</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>12.332</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>39.946</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>77.264</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>3.479</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>90.392</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>4.682</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>1.362</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -25846,7 +25846,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E265" s="5" t="n">
         <v>39.946</v>
       </c>
@@ -26948,7 +26952,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E280" s="5" t="n">
         <v>2.19</v>
       </c>
